--- a/documentacao/Testes/Caso de Teste/UC39 - LISTA DE ESPECIALISTAS.xlsx
+++ b/documentacao/Testes/Caso de Teste/UC39 - LISTA DE ESPECIALISTAS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
   <si>
     <t xml:space="preserve">CT</t>
   </si>
@@ -46,7 +46,10 @@
     <t xml:space="preserve">Evidência</t>
   </si>
   <si>
-    <t xml:space="preserve">Observações</t>
+    <t xml:space="preserve">Status v2 (OK/NOK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obervações v2</t>
   </si>
   <si>
     <t xml:space="preserve">CT03</t>
@@ -71,9 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mensagem de erro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'</t>
   </si>
   <si>
     <t xml:space="preserve">CT04</t>
@@ -263,9 +263,6 @@
     <t xml:space="preserve">Formulário preenchido</t>
   </si>
   <si>
-    <t xml:space="preserve">Mensagem padrão: “ Operação feita com sucesso.”</t>
-  </si>
-  <si>
     <t xml:space="preserve">CT11</t>
   </si>
   <si>
@@ -288,9 +285,6 @@
   </si>
   <si>
     <t xml:space="preserve">Validação específica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema salva com dados inválidos.</t>
   </si>
   <si>
     <t xml:space="preserve">CT12</t>
@@ -342,7 +336,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -379,12 +373,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -429,7 +417,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -458,10 +446,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,23 +455,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -602,8 +569,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.01"/>
@@ -640,37 +607,40 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -687,17 +657,19 @@
         <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -714,17 +686,19 @@
         <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
@@ -744,16 +718,16 @@
         <v>35</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
@@ -770,19 +744,19 @@
         <v>41</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -804,11 +778,11 @@
       <c r="H7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
@@ -830,9 +804,11 @@
       <c r="H8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>56</v>
       </c>
@@ -854,11 +830,11 @@
       <c r="H9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
@@ -878,14 +854,16 @@
         <v>68</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="120.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>70</v>
       </c>
@@ -905,94 +883,100 @@
         <v>75</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="G13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="I13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>100</v>
+      <c r="I14" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
